--- a/tools/price_track/out/2026-10.xlsx
+++ b/tools/price_track/out/2026-10.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J308"/>
+  <dimension ref="A1:J306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2883,24 +2883,24 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>google/gemma-4-26b-a4b-it:free</t>
+          <t>google/gemma-4-31b-it</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Google: Gemma 4 26B A4B  (free)</t>
+          <t>Google: Gemma 4 31B</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G83" t="n">
         <v>262144</v>
@@ -2910,44 +2910,44 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>google/gemma-4-31b-it</t>
+          <t>google/lyria-3-clip-preview</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Google: Gemma 4 31B</t>
+          <t>Google: Lyria 3 Clip Preview</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>262144</v>
+        <v>1048576</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>google/gemma-4-31b-it:free</t>
+          <t>google/lyria-3-pro-preview</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Google: Gemma 4 31B (free)</t>
+          <t>Google: Lyria 3 Pro Preview</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2957,115 +2957,115 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>262144</v>
+        <v>1048576</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>google/lyria-3-clip-preview</t>
+          <t>meta-llama/llama-3.1-70b-instruct</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Google: Lyria 3 Clip Preview</t>
+          <t>Meta: Llama 3.1 70B Instruct</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G86" t="n">
-        <v>1048576</v>
+        <v>131072</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>google/lyria-3-pro-preview</t>
+          <t>meta-llama/llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Google: Lyria 3 Pro Preview</t>
+          <t>Meta: Llama 3.1 8B Instruct</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>0.08</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.025</v>
       </c>
       <c r="G87" t="n">
-        <v>1048576</v>
+        <v>131072</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>meta-llama/llama-3.1-70b-instruct</t>
+          <t>meta-llama/llama-3.2-1b-instruct</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Meta: Llama 3.1 70B Instruct</t>
+          <t>Meta: Llama 3.2 1B Instruct</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.4</v>
+        <v>0.027</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4</v>
+        <v>0.201</v>
       </c>
       <c r="G88" t="n">
-        <v>131072</v>
+        <v>60000</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>meta-llama/llama-3.1-8b-instruct</t>
+          <t>meta-llama/llama-3.2-3b-instruct</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Meta: Llama 3.1 8B Instruct</t>
+          <t>Meta: Llama 3.2 3B Instruct</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="D89" t="n">
         <v>0.05</v>
       </c>
       <c r="E89" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0.025</v>
+        <v>0.33</v>
       </c>
       <c r="G89" t="n">
         <v>131072</v>
@@ -3075,243 +3075,249 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>meta-llama/llama-3.2-1b-instruct</t>
+          <t>meta-llama/llama-3.3-70b-instruct</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Meta: Llama 3.2 1B Instruct</t>
+          <t>Meta: Llama 3.3 70B Instruct</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.027</v>
+        <v>0.1</v>
       </c>
       <c r="E90" t="n">
-        <v>0.201</v>
+        <v>0.32</v>
       </c>
       <c r="G90" t="n">
-        <v>60000</v>
+        <v>131072</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>meta-llama/llama-3.2-3b-instruct</t>
+          <t>meta-llama/llama-4-maverick</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Meta: Llama 3.2 3B Instruct</t>
+          <t>Meta: Llama 4 Maverick</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="D91" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="F91" t="n">
         <v>0.05</v>
       </c>
-      <c r="E91" t="n">
-        <v>0.33</v>
-      </c>
       <c r="G91" t="n">
-        <v>131072</v>
+        <v>524288</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>meta-llama/llama-3.3-70b-instruct</t>
+          <t>meta-llama/llama-4-scout</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Meta: Llama 3.3 70B Instruct</t>
+          <t>Meta: Llama 4 Scout</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="D92" t="n">
         <v>0.1</v>
       </c>
       <c r="E92" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="G92" t="n">
-        <v>131072</v>
+        <v>1310720</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>meta-llama/llama-4-maverick</t>
+          <t>meta-llama/llama-guard-4-12b</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Meta: Llama 4 Maverick</t>
+          <t>Meta: Llama Guard 4 12B</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.1875</v>
+        <v>0.18</v>
       </c>
       <c r="E93" t="n">
-        <v>0.6525</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="G93" t="n">
-        <v>524288</v>
+        <v>163840</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>meta-llama/llama-4-scout</t>
+          <t>minimax/minimax-01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Meta: Llama 4 Scout</t>
+          <t>MiniMax: MiniMax-01</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="G94" t="n">
-        <v>1310720</v>
+        <v>1000192</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>meta-llama/llama-guard-4-12b</t>
+          <t>minimax/minimax-m1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Meta: Llama Guard 4 12B</t>
+          <t>MiniMax: MiniMax M1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.18</v>
+        <v>0.55</v>
       </c>
       <c r="E95" t="n">
-        <v>0.18</v>
+        <v>2.2</v>
       </c>
       <c r="G95" t="n">
-        <v>163840</v>
+        <v>1000000</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>minimax/minimax-01</t>
+          <t>minimax/minimax-m2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MiniMax: MiniMax-01</t>
+          <t>MiniMax: MiniMax M2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.2</v>
+        <v>0.255</v>
       </c>
       <c r="E96" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="G96" t="n">
-        <v>1000192</v>
+        <v>204800</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>minimax/minimax-m1</t>
+          <t>minimax/minimax-m2-her</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MiniMax: MiniMax M1</t>
+          <t>MiniMax: MiniMax M2-her</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="E97" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.03</v>
       </c>
       <c r="G97" t="n">
-        <v>1000000</v>
+        <v>65536</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>minimax/minimax-m2</t>
+          <t>minimax/minimax-m2.1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MiniMax: MiniMax M2</t>
+          <t>MiniMax: MiniMax M2.1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.255</v>
+        <v>0.3</v>
       </c>
       <c r="E98" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.03</v>
       </c>
       <c r="G98" t="n">
         <v>204800</v>
@@ -3321,17 +3327,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>minimax/minimax-m2-her</t>
+          <t>minimax/minimax-m2.5</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MiniMax: MiniMax M2-her</t>
+          <t>MiniMax: MiniMax M2.5</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3344,24 +3350,24 @@
         <v>0.03</v>
       </c>
       <c r="G99" t="n">
-        <v>65536</v>
+        <v>204800</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>minimax/minimax-m2.1</t>
+          <t>minimax/minimax-m2.7</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MiniMax: MiniMax M2.1</t>
+          <t>MiniMax: MiniMax M2.7</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3371,7 +3377,7 @@
         <v>1.2</v>
       </c>
       <c r="F100" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G100" t="n">
         <v>204800</v>
@@ -3381,17 +3387,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>minimax/minimax-m2.5</t>
+          <t>minimax/minimax-m3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MiniMax: MiniMax M2.5</t>
+          <t>MiniMax: MiniMax M3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3401,172 +3407,172 @@
         <v>1.2</v>
       </c>
       <c r="F101" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G101" t="n">
-        <v>204800</v>
+        <v>1048576</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>minimax/minimax-m2.7</t>
+          <t>minimax/minimax-m3.1-flash</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MiniMax: MiniMax M2.7</t>
+          <t>MiniMax: MiniMax M3.1 Flash</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="E102" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F102" t="n">
-        <v>0.06</v>
+        <v>0.015</v>
       </c>
       <c r="G102" t="n">
-        <v>204800</v>
+        <v>1048576</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>minimax/minimax-m3</t>
+          <t>mistralai/codestral-2508</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MiniMax: MiniMax M3</t>
+          <t>Mistral: Codestral 2508</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="D103" t="n">
         <v>0.3</v>
       </c>
       <c r="E103" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F103" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G103" t="n">
-        <v>1048576</v>
+        <v>256000</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>minimax/minimax-m3.1-flash</t>
+          <t>mistralai/devstral-2512</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MiniMax: MiniMax M3.1 Flash</t>
+          <t>Mistral: Devstral 2 2512</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="F104" t="n">
-        <v>0.015</v>
+        <v>0.04</v>
       </c>
       <c r="G104" t="n">
-        <v>1048576</v>
+        <v>262144</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mistralai/codestral-2508</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mistral: Codestral 2508</t>
+          <t>Mistral: Ministral 3 14B 2512</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E105" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="F105" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G105" t="n">
-        <v>256000</v>
+        <v>262144</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mistralai/devstral-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mistral: Devstral 2 2512</t>
+          <t>Mistral: Ministral 3 3B 2512</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="F106" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G106" t="n">
-        <v>262144</v>
+        <v>131072</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Mistral: Ministral 3 14B 2512</t>
+          <t>Mistral: Ministral 3 8B 2512</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3575,13 +3581,13 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E107" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="F107" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="G107" t="n">
         <v>262144</v>
@@ -3591,574 +3597,574 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/mistral-large</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Mistral: Ministral 3 3B 2512</t>
+          <t>Mistral Large</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
       <c r="F108" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="G108" t="n">
-        <v>131072</v>
+        <v>128000</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/mistral-large-2407</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mistral: Ministral 3 8B 2512</t>
+          <t>Mistral Large 2407</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.15</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>0.15</v>
+        <v>6</v>
       </c>
       <c r="F109" t="n">
-        <v>0.015</v>
+        <v>0.2</v>
       </c>
       <c r="G109" t="n">
-        <v>262144</v>
+        <v>131072</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>mistralai/mistral-large</t>
+          <t>mistralai/mistral-large-2512</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mistral Large</t>
+          <t>Mistral: Mistral Large 3 2512</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E110" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="F110" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G110" t="n">
-        <v>128000</v>
+        <v>262144</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>mistralai/mistral-large-2407</t>
+          <t>mistralai/mistral-large-4-0</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mistral Large 2407</t>
+          <t>Mistral: Mistral Large 4</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="E111" t="n">
-        <v>6</v>
+        <v>4.18</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="G111" t="n">
-        <v>131072</v>
+        <v>1048576</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>mistralai/mistral-large-2512</t>
+          <t>mistralai/mistral-medium-3</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mistral: Mistral Large 3 2512</t>
+          <t>Mistral: Mistral Medium 3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E112" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F112" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G112" t="n">
-        <v>262144</v>
+        <v>131072</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>mistralai/mistral-large-4-0</t>
+          <t>mistralai/mistral-medium-3-5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Mistral: Mistral Large 4</t>
+          <t>Mistral: Mistral Medium 3.5</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="E113" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0.14</v>
+        <v>7.5</v>
       </c>
       <c r="G113" t="n">
-        <v>1048576</v>
+        <v>262144</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>mistralai/mistral-medium-3</t>
+          <t>mistralai/mistral-medium-3-5:batch</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mistral: Mistral Medium 3</t>
+          <t>Mistral: Mistral Medium 3.5 (batch)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0.04</v>
+        <v>3.75</v>
       </c>
       <c r="G114" t="n">
-        <v>131072</v>
+        <v>262144</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>mistralai/mistral-medium-3-5</t>
+          <t>mistralai/mistral-medium-3.1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mistral: Mistral Medium 3.5</t>
+          <t>Mistral: Mistral Medium 3.1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="E115" t="n">
-        <v>7.5</v>
+        <v>2</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.04</v>
       </c>
       <c r="G115" t="n">
-        <v>262144</v>
+        <v>131072</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>mistralai/mistral-medium-3-5:batch</t>
+          <t>mistralai/mistral-nemo</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mistral: Mistral Medium 3.5 (batch)</t>
+          <t>Mistral: Mistral Nemo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.75</v>
+        <v>0.029</v>
       </c>
       <c r="E116" t="n">
-        <v>3.75</v>
+        <v>0.03</v>
       </c>
       <c r="G116" t="n">
-        <v>262144</v>
+        <v>131072</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>mistralai/mistral-medium-3.1</t>
+          <t>mistralai/mistral-saba</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mistral: Mistral Medium 3.1</t>
+          <t>Mistral: Saba</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E117" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="F117" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G117" t="n">
-        <v>131072</v>
+        <v>32768</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>mistralai/mistral-nemo</t>
+          <t>mistralai/mistral-small-24b-instruct-2501</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mistral: Mistral Nemo</t>
+          <t>Mistral: Mistral Small 3</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.029</v>
+        <v>0.05</v>
       </c>
       <c r="E118" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G118" t="n">
-        <v>131072</v>
+        <v>32768</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>mistralai/mistral-saba</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mistral: Saba</t>
+          <t>Mistral: Mistral Small 4</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E119" t="n">
         <v>0.6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="G119" t="n">
-        <v>32768</v>
+        <v>262144</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-24b-instruct-2501</t>
+          <t>mistralai/mistral-small-3.1-24b-instruct</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Mistral: Mistral Small 3</t>
+          <t>Mistral: Mistral Small 3.1 24B</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.05</v>
+        <v>0.351</v>
       </c>
       <c r="E120" t="n">
-        <v>0.08</v>
+        <v>0.555</v>
       </c>
       <c r="G120" t="n">
-        <v>32768</v>
+        <v>128000</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/mistral-small-3.2-24b-instruct</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mistral: Mistral Small 4</t>
+          <t>Mistral: Mistral Small 3.2 24B</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.15</v>
+        <v>0.075</v>
       </c>
       <c r="E121" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0.015</v>
+        <v>0.2</v>
       </c>
       <c r="G121" t="n">
-        <v>262144</v>
+        <v>256000</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-3.1-24b-instruct</t>
+          <t>mistralai/mixtral-8x22b-instruct</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Mistral: Mistral Small 3.1 24B</t>
+          <t>Mistral: Mixtral 8x22B Instruct</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.351</v>
+        <v>2</v>
       </c>
       <c r="E122" t="n">
-        <v>0.555</v>
+        <v>6</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.2</v>
       </c>
       <c r="G122" t="n">
-        <v>128000</v>
+        <v>65536</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-3.2-24b-instruct</t>
+          <t>mistralai/voxtral-small-24b-2507</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mistral: Mistral Small 3.2 24B</t>
+          <t>Mistral: Voxtral Small 24B 2507</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="E123" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.01</v>
       </c>
       <c r="G123" t="n">
-        <v>256000</v>
+        <v>32768</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>mistralai/mixtral-8x22b-instruct</t>
+          <t>moonshotai/kimi-k2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mistral: Mixtral 8x22B Instruct</t>
+          <t>MoonshotAI: Kimi K2 0711</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>0.57</v>
       </c>
       <c r="E124" t="n">
-        <v>6</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="G124" t="n">
-        <v>65536</v>
+        <v>131072</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>mistralai/voxtral-small-24b-2507</t>
+          <t>moonshotai/kimi-k2-0905</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mistral: Voxtral Small 24B 2507</t>
+          <t>MoonshotAI: Kimi K2 0905</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="E125" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0.01</v>
+        <v>2.5</v>
       </c>
       <c r="G125" t="n">
-        <v>32768</v>
+        <v>262144</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2</t>
+          <t>moonshotai/kimi-k2-thinking</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MoonshotAI: Kimi K2 0711</t>
+          <t>MoonshotAI: Kimi K2 Thinking</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="E126" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.15</v>
       </c>
       <c r="G126" t="n">
-        <v>131072</v>
+        <v>262144</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2-0905</t>
+          <t>moonshotai/kimi-k2.5</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MoonshotAI: Kimi K2 0905</t>
+          <t>MoonshotAI: Kimi K2.5</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E127" t="n">
         <v>2.5</v>
       </c>
+      <c r="F127" t="n">
+        <v>0.15</v>
+      </c>
       <c r="G127" t="n">
         <v>262144</v>
       </c>
@@ -4167,24 +4173,24 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2-thinking</t>
+          <t>moonshotai/kimi-k2.6</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MoonshotAI: Kimi K2 Thinking</t>
+          <t>MoonshotAI: Kimi K2.6</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="E128" t="n">
-        <v>2.5</v>
+        <v>3.41</v>
       </c>
       <c r="F128" t="n">
         <v>0.15</v>
@@ -4197,24 +4203,24 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.5</t>
+          <t>moonshotai/kimi-k2.7-code</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MoonshotAI: Kimi K2.5</t>
+          <t>MoonshotAI: Kimi K2.7 Code</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E129" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="F129" t="n">
         <v>0.15</v>
@@ -4227,72 +4233,72 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.6</t>
+          <t>moonshotai/kimi-k3</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MoonshotAI: Kimi K2.6</t>
+          <t>MoonshotAI: Kimi K3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.65</v>
+        <v>0.179</v>
       </c>
       <c r="E130" t="n">
-        <v>3.41</v>
+        <v>11.5</v>
       </c>
       <c r="F130" t="n">
-        <v>0.15</v>
+        <v>0.169</v>
       </c>
       <c r="G130" t="n">
-        <v>262144</v>
+        <v>1048576</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.7-code</t>
+          <t>moonshotai/kimi-k3.1-pro</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MoonshotAI: Kimi K2.7 Code</t>
+          <t>MoonshotAI: Kimi K3.1 Pro</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.5600000000000001</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="F131" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G131" t="n">
-        <v>262144</v>
+        <v>1048576</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k3</t>
+          <t>moonshotai/kimi-k3:batch</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MoonshotAI: Kimi K3</t>
+          <t>MoonshotAI: Kimi K3 (batch)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4301,13 +4307,13 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.189</v>
+        <v>2.28</v>
       </c>
       <c r="E132" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="F132" t="n">
-        <v>0.179</v>
+        <v>0.228</v>
       </c>
       <c r="G132" t="n">
         <v>1048576</v>
@@ -4317,207 +4323,207 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k3.1-pro</t>
+          <t>openai/gpt-3.5-turbo-0613</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MoonshotAI: Kimi K3.1 Pro</t>
+          <t>OpenAI: GPT-3.5 Turbo (older v0613)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
         <v>2</v>
       </c>
-      <c r="E133" t="n">
-        <v>10</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0.2</v>
-      </c>
       <c r="G133" t="n">
-        <v>1048576</v>
+        <v>4095</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k3:batch</t>
+          <t>openai/gpt-3.5-turbo-16k</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MoonshotAI: Kimi K3 (batch)</t>
+          <t>OpenAI: GPT-3.5 Turbo 16k</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="E134" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0.228</v>
+        <v>4</v>
       </c>
       <c r="G134" t="n">
-        <v>1048576</v>
+        <v>16385</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>openai/gpt-3.5-turbo-0613</t>
+          <t>openai/gpt-4</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-3.5 Turbo (older v0613)</t>
+          <t>OpenAI: GPT-4</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E135" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="G135" t="n">
-        <v>4095</v>
+        <v>8191</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>openai/gpt-3.5-turbo-16k</t>
+          <t>openai/gpt-4-turbo</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-3.5 Turbo 16k</t>
+          <t>OpenAI: GPT-4 Turbo</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E136" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="G136" t="n">
-        <v>16385</v>
+        <v>128000</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>openai/gpt-4</t>
+          <t>openai/gpt-4-turbo:batch</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4</t>
+          <t>OpenAI: GPT-4 Turbo (batch)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E137" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G137" t="n">
-        <v>8191</v>
+        <v>128000</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>openai/gpt-4-turbo</t>
+          <t>openai/gpt-4.1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4 Turbo</t>
+          <t>OpenAI: GPT-4.1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5</v>
       </c>
       <c r="G138" t="n">
-        <v>128000</v>
+        <v>1047576</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>openai/gpt-4-turbo:batch</t>
+          <t>openai/gpt-4.1-mini</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4 Turbo (batch)</t>
+          <t>OpenAI: GPT-4.1 Mini</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="E139" t="n">
-        <v>15</v>
+        <v>1.6</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.1</v>
       </c>
       <c r="G139" t="n">
-        <v>128000</v>
+        <v>1047576</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1</t>
+          <t>openai/gpt-4.1-mini:batch</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4.1</t>
+          <t>OpenAI: GPT-4.1 Mini (batch)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4526,13 +4532,13 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="E140" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="F140" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="G140" t="n">
         <v>1047576</v>
@@ -4542,12 +4548,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-mini</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4.1 Mini</t>
+          <t>OpenAI: GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4556,13 +4562,13 @@
         </is>
       </c>
       <c r="D141" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E141" t="n">
         <v>0.4</v>
       </c>
-      <c r="E141" t="n">
-        <v>1.6</v>
-      </c>
       <c r="F141" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="G141" t="n">
         <v>1047576</v>
@@ -4572,12 +4578,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-mini:batch</t>
+          <t>openai/gpt-4.1-nano:batch</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4.1 Mini (batch)</t>
+          <t>OpenAI: GPT-4.1 Nano (batch)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4586,13 +4592,13 @@
         </is>
       </c>
       <c r="D142" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E142" t="n">
         <v>0.2</v>
       </c>
-      <c r="E142" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F142" t="n">
-        <v>0.05</v>
+        <v>0.0125</v>
       </c>
       <c r="G142" t="n">
         <v>1047576</v>
@@ -4602,12 +4608,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>openai/gpt-4.1:batch</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4.1 Nano</t>
+          <t>OpenAI: GPT-4.1 (batch)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4616,13 +4622,13 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="F143" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="G143" t="n">
         <v>1047576</v>
@@ -4632,77 +4638,74 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano:batch</t>
+          <t>openai/gpt-4o</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4.1 Nano (batch)</t>
+          <t>OpenAI: GPT-4o</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.05</v>
+        <v>2.5</v>
       </c>
       <c r="E144" t="n">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0125</v>
+        <v>1.25</v>
       </c>
       <c r="G144" t="n">
-        <v>1047576</v>
+        <v>128000</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1:batch</t>
+          <t>openai/gpt-4o-2024-05-13</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4.1 (batch)</t>
+          <t>OpenAI: GPT-4o (2024-05-13)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E145" t="n">
-        <v>4</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0.25</v>
+        <v>15</v>
       </c>
       <c r="G145" t="n">
-        <v>1047576</v>
+        <v>128000</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>openai/gpt-4o</t>
+          <t>openai/gpt-4o-2024-08-06</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4o</t>
+          <t>OpenAI: GPT-4o (2024-08-06)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -4722,24 +4725,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>openai/gpt-4o-2024-05-13</t>
+          <t>openai/gpt-4o-2024-11-20</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4o (2024-05-13)</t>
+          <t>OpenAI: GPT-4o (2024-11-20)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E147" t="n">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1.25</v>
       </c>
       <c r="G147" t="n">
         <v>128000</v>
@@ -4749,27 +4755,27 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>openai/gpt-4o-2024-08-06</t>
+          <t>openai/gpt-4o-mini</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4o (2024-08-06)</t>
+          <t>OpenAI: GPT-4o-mini</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2.5</v>
+        <v>0.15</v>
       </c>
       <c r="E148" t="n">
-        <v>10</v>
+        <v>0.6</v>
       </c>
       <c r="F148" t="n">
-        <v>1.25</v>
+        <v>0.075</v>
       </c>
       <c r="G148" t="n">
         <v>128000</v>
@@ -4779,27 +4785,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>openai/gpt-4o-2024-11-20</t>
+          <t>openai/gpt-4o-mini-2024-07-18</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4o (2024-11-20)</t>
+          <t>OpenAI: GPT-4o-mini (2024-07-18)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2.5</v>
+        <v>0.15</v>
       </c>
       <c r="E149" t="n">
-        <v>10</v>
+        <v>0.6</v>
       </c>
       <c r="F149" t="n">
-        <v>1.25</v>
+        <v>0.075</v>
       </c>
       <c r="G149" t="n">
         <v>128000</v>
@@ -4809,12 +4815,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>openai/gpt-4o-mini</t>
+          <t>openai/gpt-4o-mini:batch</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4o-mini</t>
+          <t>OpenAI: GPT-4o-mini (batch)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4823,13 +4829,13 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.15</v>
+        <v>0.075</v>
       </c>
       <c r="E150" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F150" t="n">
-        <v>0.075</v>
+        <v>0.0375</v>
       </c>
       <c r="G150" t="n">
         <v>128000</v>
@@ -4839,27 +4845,27 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>openai/gpt-4o-mini-2024-07-18</t>
+          <t>openai/gpt-4o:batch</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4o-mini (2024-07-18)</t>
+          <t>OpenAI: GPT-4o (batch)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.15</v>
+        <v>1.25</v>
       </c>
       <c r="E151" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="F151" t="n">
-        <v>0.075</v>
+        <v>0.625</v>
       </c>
       <c r="G151" t="n">
         <v>128000</v>
@@ -4869,87 +4875,87 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>openai/gpt-4o-mini:batch</t>
+          <t>openai/gpt-5</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4o-mini (batch)</t>
+          <t>OpenAI: GPT-5</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.075</v>
+        <v>1.25</v>
       </c>
       <c r="E152" t="n">
-        <v>0.3</v>
+        <v>10</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0375</v>
+        <v>0.125</v>
       </c>
       <c r="G152" t="n">
-        <v>128000</v>
+        <v>400000</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>openai/gpt-4o:batch</t>
+          <t>openai/gpt-5-image</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-4o (batch)</t>
+          <t>OpenAI: GPT-5 Image</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="D153" t="n">
+        <v>10</v>
+      </c>
+      <c r="E153" t="n">
+        <v>10</v>
+      </c>
+      <c r="F153" t="n">
         <v>1.25</v>
       </c>
-      <c r="E153" t="n">
-        <v>5</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0.625</v>
-      </c>
       <c r="G153" t="n">
-        <v>128000</v>
+        <v>400000</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>openai/gpt-5</t>
+          <t>openai/gpt-5-image-mini</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5</t>
+          <t>OpenAI: GPT-5 Image Mini</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="E154" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F154" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="G154" t="n">
         <v>400000</v>
@@ -4959,27 +4965,27 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>openai/gpt-5-image</t>
+          <t>openai/gpt-5-mini</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5 Image</t>
+          <t>OpenAI: GPT-5 Mini</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>10</v>
+        <v>0.25</v>
       </c>
       <c r="E155" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F155" t="n">
-        <v>1.25</v>
+        <v>0.025</v>
       </c>
       <c r="G155" t="n">
         <v>400000</v>
@@ -4989,27 +4995,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>openai/gpt-5-image-mini</t>
+          <t>openai/gpt-5-mini:batch</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5 Image Mini</t>
+          <t>OpenAI: GPT-5 Mini (batch)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2.5</v>
+        <v>0.125</v>
       </c>
       <c r="E156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>0.25</v>
+        <v>0.0125</v>
       </c>
       <c r="G156" t="n">
         <v>400000</v>
@@ -5019,12 +5025,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>openai/gpt-5-mini</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5 Mini</t>
+          <t>OpenAI: GPT-5 Nano</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5033,13 +5039,13 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="E157" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="F157" t="n">
-        <v>0.025</v>
+        <v>0.005</v>
       </c>
       <c r="G157" t="n">
         <v>400000</v>
@@ -5049,12 +5055,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>openai/gpt-5-mini:batch</t>
+          <t>openai/gpt-5-nano:batch</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5 Mini (batch)</t>
+          <t>OpenAI: GPT-5 Nano (batch)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5063,13 +5069,13 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.125</v>
+        <v>0.025</v>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0125</v>
+        <v>0.0025</v>
       </c>
       <c r="G158" t="n">
         <v>400000</v>
@@ -5079,27 +5085,24 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-5-pro</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5 Nano</t>
+          <t>OpenAI: GPT-5 Pro</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.05</v>
+        <v>15</v>
       </c>
       <c r="E159" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0.005</v>
+        <v>120</v>
       </c>
       <c r="G159" t="n">
         <v>400000</v>
@@ -5109,27 +5112,24 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano:batch</t>
+          <t>openai/gpt-5-pro:batch</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5 Nano (batch)</t>
+          <t>OpenAI: GPT-5 Pro (batch)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.025</v>
+        <v>7.5</v>
       </c>
       <c r="E160" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0.0025</v>
+        <v>60</v>
       </c>
       <c r="G160" t="n">
         <v>400000</v>
@@ -5139,24 +5139,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>openai/gpt-5-pro</t>
+          <t>openai/gpt-5.1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5 Pro</t>
+          <t>OpenAI: GPT-5.1</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>15</v>
+        <v>1.25</v>
       </c>
       <c r="E161" t="n">
-        <v>120</v>
+        <v>10</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.125</v>
       </c>
       <c r="G161" t="n">
         <v>400000</v>
@@ -5166,24 +5169,27 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>openai/gpt-5-pro:batch</t>
+          <t>openai/gpt-5.1-codex</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5 Pro (batch)</t>
+          <t>OpenAI: GPT-5.1-Codex</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>7.5</v>
+        <v>1.25</v>
       </c>
       <c r="E162" t="n">
-        <v>60</v>
+        <v>10</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.13</v>
       </c>
       <c r="G162" t="n">
         <v>400000</v>
@@ -5193,17 +5199,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>openai/gpt-5.1</t>
+          <t>openai/gpt-5.1-codex-max</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.1</t>
+          <t>OpenAI: GPT-5.1-Codex-Max</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -5223,12 +5229,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>openai/gpt-5.1-codex</t>
+          <t>openai/gpt-5.1-codex-mini</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.1-Codex</t>
+          <t>OpenAI: GPT-5.1-Codex-Mini</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5237,13 +5243,13 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="E164" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F164" t="n">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="G164" t="n">
         <v>400000</v>
@@ -5253,27 +5259,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>openai/gpt-5.1-codex-max</t>
+          <t>openai/gpt-5.1:batch</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.1-Codex-Max</t>
+          <t>OpenAI: GPT-5.1 (batch)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1.25</v>
+        <v>0.625</v>
       </c>
       <c r="E165" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F165" t="n">
-        <v>0.125</v>
+        <v>0.0625</v>
       </c>
       <c r="G165" t="n">
         <v>400000</v>
@@ -5283,27 +5289,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>openai/gpt-5.1-codex-mini</t>
+          <t>openai/gpt-5.2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.1-Codex-Mini</t>
+          <t>OpenAI: GPT-5.2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="E166" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F166" t="n">
-        <v>0.03</v>
+        <v>0.175</v>
       </c>
       <c r="G166" t="n">
         <v>400000</v>
@@ -5313,47 +5319,47 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>openai/gpt-5.1:batch</t>
+          <t>openai/gpt-5.2-chat</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.1 (batch)</t>
+          <t>OpenAI: GPT-5.2 Chat</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.625</v>
+        <v>1.75</v>
       </c>
       <c r="E167" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0625</v>
+        <v>0.175</v>
       </c>
       <c r="G167" t="n">
-        <v>400000</v>
+        <v>128000</v>
       </c>
       <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>openai/gpt-5.2</t>
+          <t>openai/gpt-5.2-codex</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.2</t>
+          <t>OpenAI: GPT-5.2-Codex</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -5373,12 +5379,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>openai/gpt-5.2-chat</t>
+          <t>openai/gpt-5.2-pro</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.2 Chat</t>
+          <t>OpenAI: GPT-5.2 Pro</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5387,43 +5393,37 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1.75</v>
+        <v>21</v>
       </c>
       <c r="E169" t="n">
-        <v>14</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0.175</v>
+        <v>168</v>
       </c>
       <c r="G169" t="n">
-        <v>128000</v>
+        <v>400000</v>
       </c>
       <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>openai/gpt-5.2-codex</t>
+          <t>openai/gpt-5.2-pro:batch</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.2-Codex</t>
+          <t>OpenAI: GPT-5.2 Pro (batch)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1.75</v>
+        <v>10.5</v>
       </c>
       <c r="E170" t="n">
-        <v>14</v>
-      </c>
-      <c r="F170" t="n">
-        <v>0.175</v>
+        <v>84</v>
       </c>
       <c r="G170" t="n">
         <v>400000</v>
@@ -5433,12 +5433,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>openai/gpt-5.2-pro</t>
+          <t>openai/gpt-5.2:batch</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.2 Pro</t>
+          <t>OpenAI: GPT-5.2 (batch)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5447,10 +5447,13 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>21</v>
+        <v>0.875</v>
       </c>
       <c r="E171" t="n">
-        <v>168</v>
+        <v>7</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.08749999999999999</v>
       </c>
       <c r="G171" t="n">
         <v>400000</v>
@@ -5460,24 +5463,27 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>openai/gpt-5.2-pro:batch</t>
+          <t>openai/gpt-5.3-codex</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.2 Pro (batch)</t>
+          <t>OpenAI: GPT-5.3-Codex</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>10.5</v>
+        <v>1.75</v>
       </c>
       <c r="E172" t="n">
-        <v>84</v>
+        <v>14</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.175</v>
       </c>
       <c r="G172" t="n">
         <v>400000</v>
@@ -5487,132 +5493,132 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>openai/gpt-5.2:batch</t>
+          <t>openai/gpt-5.4</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.2 (batch)</t>
+          <t>OpenAI: GPT-5.4</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0.875</v>
+        <v>2.5</v>
       </c>
       <c r="E173" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F173" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G173" t="n">
-        <v>400000</v>
+        <v>1050000</v>
       </c>
       <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>openai/gpt-5.3-codex</t>
+          <t>openai/gpt-5.4-image-2</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.3-Codex</t>
+          <t>OpenAI: GPT-5.4 Image 2</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1.75</v>
+        <v>8</v>
       </c>
       <c r="E174" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F174" t="n">
-        <v>0.175</v>
+        <v>2</v>
       </c>
       <c r="G174" t="n">
-        <v>400000</v>
+        <v>272000</v>
       </c>
       <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4</t>
+          <t>openai/gpt-5.4-mini</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.4</t>
+          <t>OpenAI: GPT-5.4 Mini</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="E175" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="F175" t="n">
-        <v>0.25</v>
+        <v>0.075</v>
       </c>
       <c r="G175" t="n">
-        <v>1050000</v>
+        <v>400000</v>
       </c>
       <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-image-2</t>
+          <t>openai/gpt-5.4-mini:batch</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.4 Image 2</t>
+          <t>OpenAI: GPT-5.4 Mini (batch)</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>8</v>
+        <v>0.375</v>
       </c>
       <c r="E176" t="n">
-        <v>15</v>
+        <v>2.25</v>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>0.0375</v>
       </c>
       <c r="G176" t="n">
-        <v>272000</v>
+        <v>400000</v>
       </c>
       <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-mini</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.4 Mini</t>
+          <t>OpenAI: GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5621,13 +5627,13 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="E177" t="n">
-        <v>4.5</v>
+        <v>1.25</v>
       </c>
       <c r="F177" t="n">
-        <v>0.075</v>
+        <v>0.02</v>
       </c>
       <c r="G177" t="n">
         <v>400000</v>
@@ -5637,12 +5643,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-mini:batch</t>
+          <t>openai/gpt-5.4-nano:batch</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.4 Mini (batch)</t>
+          <t>OpenAI: GPT-5.4 Nano (batch)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5651,13 +5657,13 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.375</v>
+        <v>0.1</v>
       </c>
       <c r="E178" t="n">
-        <v>2.25</v>
+        <v>0.625</v>
       </c>
       <c r="F178" t="n">
-        <v>0.0375</v>
+        <v>0.01</v>
       </c>
       <c r="G178" t="n">
         <v>400000</v>
@@ -5667,72 +5673,66 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5.4-pro</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.4 Nano</t>
+          <t>OpenAI: GPT-5.4 Pro</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.2</v>
+        <v>30</v>
       </c>
       <c r="E179" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0.02</v>
+        <v>180</v>
       </c>
       <c r="G179" t="n">
-        <v>400000</v>
+        <v>1050000</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano:batch</t>
+          <t>openai/gpt-5.4-pro:batch</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.4 Nano (batch)</t>
+          <t>OpenAI: GPT-5.4 Pro (batch)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.1</v>
+        <v>15</v>
       </c>
       <c r="E180" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0.01</v>
+        <v>90</v>
       </c>
       <c r="G180" t="n">
-        <v>400000</v>
+        <v>1050000</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-pro</t>
+          <t>openai/gpt-5.4:batch</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.4 Pro</t>
+          <t>OpenAI: GPT-5.4 (batch)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5741,10 +5741,13 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>30</v>
+        <v>1.25</v>
       </c>
       <c r="E181" t="n">
-        <v>180</v>
+        <v>7.5</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.125</v>
       </c>
       <c r="G181" t="n">
         <v>1050000</v>
@@ -5754,24 +5757,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-pro:batch</t>
+          <t>openai/gpt-5.5</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.4 Pro (batch)</t>
+          <t>OpenAI: GPT-5.5</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E182" t="n">
-        <v>90</v>
+        <v>30</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.5</v>
       </c>
       <c r="G182" t="n">
         <v>1050000</v>
@@ -5781,27 +5787,24 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4:batch</t>
+          <t>openai/gpt-5.5-pro</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.4 (batch)</t>
+          <t>OpenAI: GPT-5.5 Pro</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1.25</v>
+        <v>30</v>
       </c>
       <c r="E183" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F183" t="n">
-        <v>0.125</v>
+        <v>180</v>
       </c>
       <c r="G183" t="n">
         <v>1050000</v>
@@ -5811,12 +5814,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>openai/gpt-5.5</t>
+          <t>openai/gpt-5.5-pro:batch</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.5</t>
+          <t>OpenAI: GPT-5.5 Pro (batch)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5825,13 +5828,10 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E184" t="n">
-        <v>30</v>
-      </c>
-      <c r="F184" t="n">
-        <v>0.5</v>
+        <v>90</v>
       </c>
       <c r="G184" t="n">
         <v>1050000</v>
@@ -5841,12 +5841,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>openai/gpt-5.5-pro</t>
+          <t>openai/gpt-5.5:batch</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.5 Pro</t>
+          <t>OpenAI: GPT-5.5 (batch)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5855,10 +5855,13 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>30</v>
+        <v>2.5</v>
       </c>
       <c r="E185" t="n">
-        <v>180</v>
+        <v>15</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.25</v>
       </c>
       <c r="G185" t="n">
         <v>1050000</v>
@@ -5868,24 +5871,27 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>openai/gpt-5.5-pro:batch</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.5 Pro (batch)</t>
+          <t>OpenAI: GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>15</v>
+        <v>0.2</v>
       </c>
       <c r="E186" t="n">
-        <v>90</v>
+        <v>1.2</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.02</v>
       </c>
       <c r="G186" t="n">
         <v>1050000</v>
@@ -5895,27 +5901,27 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>openai/gpt-5.5:batch</t>
+          <t>openai/gpt-5.6-luna-pro</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.5 (batch)</t>
+          <t>OpenAI: GPT-5.6 Luna Pro</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="E187" t="n">
-        <v>15</v>
+        <v>1.2</v>
       </c>
       <c r="F187" t="n">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
       <c r="G187" t="n">
         <v>1050000</v>
@@ -5925,12 +5931,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.6-luna-pro:batch</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Luna</t>
+          <t>OpenAI: GPT-5.6 Luna Pro (batch)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5939,13 +5945,13 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E188" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F188" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G188" t="n">
         <v>1050000</v>
@@ -5955,12 +5961,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna-pro</t>
+          <t>openai/gpt-5.6-luna:batch</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Luna Pro</t>
+          <t>OpenAI: GPT-5.6 Luna (batch)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5969,13 +5975,13 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E189" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F189" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G189" t="n">
         <v>1050000</v>
@@ -5985,12 +5991,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna-pro:batch</t>
+          <t>openai/gpt-5.6-sol</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Luna Pro (batch)</t>
+          <t>OpenAI: GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5999,13 +6005,13 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="E190" t="n">
-        <v>0.6</v>
+        <v>20</v>
       </c>
       <c r="F190" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="G190" t="n">
         <v>1050000</v>
@@ -6015,12 +6021,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna:batch</t>
+          <t>openai/gpt-5.6-sol-pro</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Luna (batch)</t>
+          <t>OpenAI: GPT-5.6 Sol Pro</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6029,13 +6035,13 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="E191" t="n">
-        <v>0.6</v>
+        <v>20</v>
       </c>
       <c r="F191" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="G191" t="n">
         <v>1050000</v>
@@ -6045,12 +6051,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-sol</t>
+          <t>openai/gpt-5.6-sol-pro:batch</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Sol</t>
+          <t>OpenAI: GPT-5.6 Sol Pro (batch)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6059,13 +6065,13 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E192" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F192" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G192" t="n">
         <v>1050000</v>
@@ -6075,12 +6081,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-sol-pro</t>
+          <t>openai/gpt-5.6-sol:batch</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Sol Pro</t>
+          <t>OpenAI: GPT-5.6 Sol (batch)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6089,13 +6095,13 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E193" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F193" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G193" t="n">
         <v>1050000</v>
@@ -6105,12 +6111,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-sol-pro:batch</t>
+          <t>openai/gpt-5.6-terra</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Sol Pro (batch)</t>
+          <t>OpenAI: GPT-5.6 Terra</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6122,7 +6128,7 @@
         <v>2</v>
       </c>
       <c r="E194" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F194" t="n">
         <v>0.2</v>
@@ -6135,12 +6141,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-sol:batch</t>
+          <t>openai/gpt-5.6-terra-pro</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Sol (batch)</t>
+          <t>OpenAI: GPT-5.6 Terra Pro</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6152,7 +6158,7 @@
         <v>2</v>
       </c>
       <c r="E195" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F195" t="n">
         <v>0.2</v>
@@ -6165,12 +6171,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-terra</t>
+          <t>openai/gpt-5.6-terra-pro:batch</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Terra</t>
+          <t>OpenAI: GPT-5.6 Terra Pro (batch)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6179,13 +6185,13 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F196" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G196" t="n">
         <v>1050000</v>
@@ -6195,12 +6201,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-terra-pro</t>
+          <t>openai/gpt-5.6-terra:batch</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Terra Pro</t>
+          <t>OpenAI: GPT-5.6 Terra (batch)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6209,13 +6215,13 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E197" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F197" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G197" t="n">
         <v>1050000</v>
@@ -6225,57 +6231,57 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-terra-pro:batch</t>
+          <t>openai/gpt-5:batch</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Terra Pro (batch)</t>
+          <t>OpenAI: GPT-5 (batch)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="E198" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>0.1</v>
+        <v>0.0625</v>
       </c>
       <c r="G198" t="n">
-        <v>1050000</v>
+        <v>400000</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-terra:batch</t>
+          <t>openai/gpt-6-astra</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5.6 Terra (batch)</t>
+          <t>OpenAI: GPT-6 Astra</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D199" t="n">
+        <v>10</v>
+      </c>
+      <c r="E199" t="n">
+        <v>50</v>
+      </c>
+      <c r="F199" t="n">
         <v>1</v>
-      </c>
-      <c r="E199" t="n">
-        <v>6</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0.1</v>
       </c>
       <c r="G199" t="n">
         <v>1050000</v>
@@ -6285,42 +6291,42 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>openai/gpt-5:batch</t>
+          <t>openai/gpt-6-astra-pro</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-5 (batch)</t>
+          <t>OpenAI: GPT-6 Astra Pro</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.625</v>
+        <v>10</v>
       </c>
       <c r="E200" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F200" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="G200" t="n">
-        <v>400000</v>
+        <v>1050000</v>
       </c>
       <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>openai/gpt-6-astra</t>
+          <t>openai/gpt-6-astra-pro:batch</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Astra</t>
+          <t>OpenAI: GPT-6 Astra Pro (batch)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6329,13 +6335,13 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E201" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G201" t="n">
         <v>1050000</v>
@@ -6345,12 +6351,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>openai/gpt-6-astra-pro</t>
+          <t>openai/gpt-6-astra:batch</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Astra Pro</t>
+          <t>OpenAI: GPT-6 Astra (batch)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6359,13 +6365,13 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E202" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G202" t="n">
         <v>1050000</v>
@@ -6375,27 +6381,27 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>openai/gpt-6-astra-pro:batch</t>
+          <t>openai/gpt-6-luna</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Astra Pro (batch)</t>
+          <t>OpenAI: GPT-6 Luna</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="E203" t="n">
-        <v>25</v>
+        <v>0.5</v>
       </c>
       <c r="F203" t="n">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="G203" t="n">
         <v>1050000</v>
@@ -6405,27 +6411,27 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>openai/gpt-6-astra:batch</t>
+          <t>openai/gpt-6-luna-pro</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Astra (batch)</t>
+          <t>OpenAI: GPT-6 Luna Pro</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="E204" t="n">
-        <v>25</v>
+        <v>0.5</v>
       </c>
       <c r="F204" t="n">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="G204" t="n">
         <v>1050000</v>
@@ -6435,12 +6441,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna</t>
+          <t>openai/gpt-6-luna-pro:batch</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Luna</t>
+          <t>OpenAI: GPT-6 Luna Pro (batch)</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6449,13 +6455,13 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E205" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F205" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="G205" t="n">
         <v>1050000</v>
@@ -6465,12 +6471,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna-pro</t>
+          <t>openai/gpt-6-luna:batch</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Luna Pro</t>
+          <t>OpenAI: GPT-6 Luna (batch)</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6479,13 +6485,13 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E206" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F206" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="G206" t="n">
         <v>1050000</v>
@@ -6495,12 +6501,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna-pro:batch</t>
+          <t>openai/gpt-6-sol</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Luna Pro (batch)</t>
+          <t>OpenAI: GPT-6 Sol</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6509,13 +6515,13 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="E207" t="n">
-        <v>0.25</v>
+        <v>10</v>
       </c>
       <c r="F207" t="n">
-        <v>0.005</v>
+        <v>0.2</v>
       </c>
       <c r="G207" t="n">
         <v>1050000</v>
@@ -6525,12 +6531,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna:batch</t>
+          <t>openai/gpt-6-sol-pro</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Luna (batch)</t>
+          <t>OpenAI: GPT-6 Sol Pro</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6539,13 +6545,13 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="E208" t="n">
-        <v>0.25</v>
+        <v>10</v>
       </c>
       <c r="F208" t="n">
-        <v>0.005</v>
+        <v>0.2</v>
       </c>
       <c r="G208" t="n">
         <v>1050000</v>
@@ -6555,12 +6561,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>openai/gpt-6-sol</t>
+          <t>openai/gpt-6-sol-pro:batch</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Sol</t>
+          <t>OpenAI: GPT-6 Sol Pro (batch)</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6569,13 +6575,13 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F209" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G209" t="n">
         <v>1050000</v>
@@ -6585,12 +6591,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>openai/gpt-6-sol-pro</t>
+          <t>openai/gpt-6-sol:batch</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Sol Pro</t>
+          <t>OpenAI: GPT-6 Sol (batch)</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6599,13 +6605,13 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F210" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G210" t="n">
         <v>1050000</v>
@@ -6615,24 +6621,24 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>openai/gpt-6-sol-pro:batch</t>
+          <t>openai/gpt-6.1-sol</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Sol Pro (batch)</t>
+          <t>OpenAI: GPT-6.1 Sol</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E211" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F211" t="n">
         <v>0.1</v>
@@ -6645,24 +6651,24 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>openai/gpt-6-sol:batch</t>
+          <t>openai/gpt-6.1-sol-pro</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6 Sol (batch)</t>
+          <t>OpenAI: GPT-6.1 Sol Pro</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E212" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F212" t="n">
         <v>0.1</v>
@@ -6675,12 +6681,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>openai/gpt-6.1-sol</t>
+          <t>openai/gpt-6.1-sol-pro:batch</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6.1 Sol</t>
+          <t>OpenAI: GPT-6.1 Sol Pro (batch)</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6689,13 +6695,13 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E213" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F213" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G213" t="n">
         <v>1050000</v>
@@ -6705,12 +6711,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>openai/gpt-6.1-sol-pro</t>
+          <t>openai/gpt-6.1-sol:batch</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6.1 Sol Pro</t>
+          <t>OpenAI: GPT-6.1 Sol (batch)</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6719,13 +6725,13 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E214" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F214" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G214" t="n">
         <v>1050000</v>
@@ -6735,17 +6741,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>openai/gpt-6.1-sol-pro:batch</t>
+          <t>openai/gpt-6.1-terra</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6.1 Sol Pro (batch)</t>
+          <t>OpenAI: GPT-6.1 Terra</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -6765,17 +6771,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>openai/gpt-6.1-sol:batch</t>
+          <t>openai/gpt-6.1-terra-pro</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6.1 Sol (batch)</t>
+          <t>OpenAI: GPT-6.1 Terra Pro</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -6795,12 +6801,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>openai/gpt-6.1-terra</t>
+          <t>openai/gpt-6.1-terra-pro:batch</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6.1 Terra</t>
+          <t>OpenAI: GPT-6.1 Terra Pro (batch)</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6809,13 +6815,13 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E217" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="F217" t="n">
-        <v>0.05</v>
+        <v>0.025</v>
       </c>
       <c r="G217" t="n">
         <v>1050000</v>
@@ -6825,12 +6831,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>openai/gpt-6.1-terra-pro</t>
+          <t>openai/gpt-6.1-terra:batch</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6.1 Terra Pro</t>
+          <t>OpenAI: GPT-6.1 Terra (batch)</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6839,13 +6845,13 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E218" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="F218" t="n">
-        <v>0.05</v>
+        <v>0.025</v>
       </c>
       <c r="G218" t="n">
         <v>1050000</v>
@@ -6855,156 +6861,153 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>openai/gpt-6.1-terra-pro:batch</t>
+          <t>openai/gpt-audio</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6.1 Terra Pro (batch)</t>
+          <t>OpenAI: GPT Audio</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="E219" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F219" t="n">
-        <v>0.025</v>
+        <v>10</v>
       </c>
       <c r="G219" t="n">
-        <v>1050000</v>
+        <v>128000</v>
       </c>
       <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>openai/gpt-6.1-terra:batch</t>
+          <t>openai/gpt-audio-mini</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>OpenAI: GPT-6.1 Terra (batch)</t>
+          <t>OpenAI: GPT Audio Mini</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E220" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F220" t="n">
-        <v>0.025</v>
+        <v>2.4</v>
       </c>
       <c r="G220" t="n">
-        <v>1050000</v>
+        <v>128000</v>
       </c>
       <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>openai/gpt-audio</t>
+          <t>openai/gpt-chat-latest</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>OpenAI: GPT Audio</t>
+          <t>OpenAI: GPT Chat Latest</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E221" t="n">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.5</v>
       </c>
       <c r="G221" t="n">
-        <v>128000</v>
+        <v>400000</v>
       </c>
       <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>openai/gpt-audio-mini</t>
+          <t>openai/gpt-oss-120b</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>OpenAI: GPT Audio Mini</t>
+          <t>OpenAI: gpt-oss-120b</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="D222" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E222" t="n">
         <v>0.6</v>
       </c>
-      <c r="E222" t="n">
-        <v>2.4</v>
+      <c r="F222" t="n">
+        <v>0.075</v>
       </c>
       <c r="G222" t="n">
-        <v>128000</v>
+        <v>131072</v>
       </c>
       <c r="H222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>openai/gpt-chat-latest</t>
+          <t>openai/gpt-oss-120b:batch</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>OpenAI: GPT Chat Latest</t>
+          <t>OpenAI: gpt-oss-120b (batch)</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>5</v>
+        <v>0.0296</v>
       </c>
       <c r="E223" t="n">
-        <v>30</v>
-      </c>
-      <c r="F223" t="n">
-        <v>0.5</v>
+        <v>0.136</v>
       </c>
       <c r="G223" t="n">
-        <v>400000</v>
+        <v>131072</v>
       </c>
       <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>openai/gpt-oss-120b</t>
+          <t>openai/gpt-oss-20b</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>OpenAI: gpt-oss-120b</t>
+          <t>OpenAI: gpt-oss-20b</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7013,13 +7016,13 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0.15</v>
+        <v>0.018</v>
       </c>
       <c r="E224" t="n">
-        <v>0.6</v>
+        <v>0.09</v>
       </c>
       <c r="F224" t="n">
-        <v>0.075</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G224" t="n">
         <v>131072</v>
@@ -7029,12 +7032,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>openai/gpt-oss-120b:batch</t>
+          <t>openai/gpt-oss-20b:batch</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>OpenAI: gpt-oss-120b (batch)</t>
+          <t>OpenAI: gpt-oss-20b (batch)</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7043,10 +7046,10 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.0296</v>
+        <v>0.024</v>
       </c>
       <c r="E225" t="n">
-        <v>0.136</v>
+        <v>0.112</v>
       </c>
       <c r="G225" t="n">
         <v>131072</v>
@@ -7056,27 +7059,27 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>openai/gpt-oss-20b</t>
+          <t>openai/gpt-oss-safeguard-20b</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>OpenAI: gpt-oss-20b</t>
+          <t>OpenAI: gpt-oss-safeguard-20b</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0.018</v>
+        <v>0.075</v>
       </c>
       <c r="E226" t="n">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="F226" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0375</v>
       </c>
       <c r="G226" t="n">
         <v>131072</v>
@@ -7086,84 +7089,84 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>openai/gpt-oss-20b:batch</t>
+          <t>openai/o1</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>OpenAI: gpt-oss-20b (batch)</t>
+          <t>OpenAI: o1</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.024</v>
+        <v>15</v>
       </c>
       <c r="E227" t="n">
-        <v>0.112</v>
+        <v>60</v>
+      </c>
+      <c r="F227" t="n">
+        <v>7.5</v>
       </c>
       <c r="G227" t="n">
-        <v>131072</v>
+        <v>200000</v>
       </c>
       <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>openai/gpt-oss-safeguard-20b</t>
+          <t>openai/o1-pro</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>OpenAI: gpt-oss-safeguard-20b</t>
+          <t>OpenAI: o1-pro</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.075</v>
+        <v>150</v>
       </c>
       <c r="E228" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F228" t="n">
-        <v>0.0375</v>
+        <v>600</v>
       </c>
       <c r="G228" t="n">
-        <v>131072</v>
+        <v>200000</v>
       </c>
       <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>openai/o1</t>
+          <t>openai/o3</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>OpenAI: o1</t>
+          <t>OpenAI: o3</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E229" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F229" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="G229" t="n">
         <v>200000</v>
@@ -7173,24 +7176,27 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>openai/o1-pro</t>
+          <t>openai/o3-mini</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>OpenAI: o1-pro</t>
+          <t>OpenAI: o3 Mini</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>150</v>
+        <v>1.1</v>
       </c>
       <c r="E230" t="n">
-        <v>600</v>
+        <v>4.4</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0.55</v>
       </c>
       <c r="G230" t="n">
         <v>200000</v>
@@ -7200,27 +7206,27 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>openai/o3</t>
+          <t>openai/o3-mini-high</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>OpenAI: o3</t>
+          <t>OpenAI: o3 Mini High</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="E231" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="F231" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G231" t="n">
         <v>200000</v>
@@ -7230,12 +7236,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>openai/o3-mini</t>
+          <t>openai/o3-mini:batch</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>OpenAI: o3 Mini</t>
+          <t>OpenAI: o3 Mini (batch)</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7244,13 +7250,13 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1.1</v>
+        <v>0.55</v>
       </c>
       <c r="E232" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="F232" t="n">
-        <v>0.55</v>
+        <v>0.275</v>
       </c>
       <c r="G232" t="n">
         <v>200000</v>
@@ -7260,27 +7266,24 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>openai/o3-mini-high</t>
+          <t>openai/o3-pro</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>OpenAI: o3 Mini High</t>
+          <t>OpenAI: o3 Pro</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1.1</v>
+        <v>20</v>
       </c>
       <c r="E233" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F233" t="n">
-        <v>0.55</v>
+        <v>80</v>
       </c>
       <c r="G233" t="n">
         <v>200000</v>
@@ -7290,27 +7293,27 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>openai/o3-mini:batch</t>
+          <t>openai/o3:batch</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>OpenAI: o3 Mini (batch)</t>
+          <t>OpenAI: o3 (batch)</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="E234" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="F234" t="n">
-        <v>0.275</v>
+        <v>0.25</v>
       </c>
       <c r="G234" t="n">
         <v>200000</v>
@@ -7320,24 +7323,27 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>openai/o3-pro</t>
+          <t>openai/o4-mini</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>OpenAI: o3 Pro</t>
+          <t>OpenAI: o4 Mini</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>20</v>
+        <v>1.1</v>
       </c>
       <c r="E235" t="n">
-        <v>80</v>
+        <v>4.4</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0.275</v>
       </c>
       <c r="G235" t="n">
         <v>200000</v>
@@ -7347,12 +7353,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>openai/o3:batch</t>
+          <t>openai/o4-mini-high</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>OpenAI: o3 (batch)</t>
+          <t>OpenAI: o4 Mini High</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7361,13 +7367,13 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="E236" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="F236" t="n">
-        <v>0.25</v>
+        <v>0.275</v>
       </c>
       <c r="G236" t="n">
         <v>200000</v>
@@ -7377,12 +7383,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>openai/o4-mini</t>
+          <t>openai/o4-mini:batch</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>OpenAI: o4 Mini</t>
+          <t>OpenAI: o4 Mini (batch)</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7391,13 +7397,13 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1.1</v>
+        <v>0.55</v>
       </c>
       <c r="E237" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="F237" t="n">
-        <v>0.275</v>
+        <v>0.1375</v>
       </c>
       <c r="G237" t="n">
         <v>200000</v>
@@ -7407,84 +7413,78 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>openai/o4-mini-high</t>
+          <t>qwen/qwen-2.5-72b-instruct</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>OpenAI: o4 Mini High</t>
+          <t>Qwen2.5 72B Instruct</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1.1</v>
+        <v>0.36</v>
       </c>
       <c r="E238" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F238" t="n">
-        <v>0.275</v>
+        <v>0.4</v>
       </c>
       <c r="G238" t="n">
-        <v>200000</v>
+        <v>32768</v>
       </c>
       <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>openai/o4-mini:batch</t>
+          <t>qwen/qwen-2.5-7b-instruct</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>OpenAI: o4 Mini (batch)</t>
+          <t>Qwen: Qwen2.5 7B Instruct</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>0.55</v>
+        <v>0.1</v>
       </c>
       <c r="E239" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F239" t="n">
-        <v>0.1375</v>
+        <v>0.2</v>
       </c>
       <c r="G239" t="n">
-        <v>200000</v>
+        <v>32768</v>
       </c>
       <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>qwen/qwen-2.5-72b-instruct</t>
+          <t>qwen/qwen-2.5-coder-32b-instruct</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Qwen2.5 72B Instruct</t>
+          <t>Qwen2.5 Coder 32B Instruct</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0.36</v>
+        <v>0.66</v>
       </c>
       <c r="E240" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G240" t="n">
         <v>32768</v>
@@ -7494,207 +7494,207 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>qwen/qwen-2.5-7b-instruct</t>
+          <t>qwen/qwen-plus</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Qwen: Qwen2.5 7B Instruct</t>
+          <t>Qwen: Qwen-Plus</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="E241" t="n">
-        <v>0.2</v>
+        <v>0.78</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0.052</v>
       </c>
       <c r="G241" t="n">
-        <v>32768</v>
+        <v>1000000</v>
       </c>
       <c r="H241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>qwen/qwen-2.5-coder-32b-instruct</t>
+          <t>qwen/qwen2.5-vl-72b-instruct</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Qwen2.5 Coder 32B Instruct</t>
+          <t>Qwen: Qwen2.5 VL 72B Instruct</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="E242" t="n">
         <v>1</v>
       </c>
+      <c r="F242" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G242" t="n">
-        <v>32768</v>
+        <v>128000</v>
       </c>
       <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>qwen/qwen-plus</t>
+          <t>qwen/qwen3-14b</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Qwen: Qwen-Plus</t>
+          <t>Qwen: Qwen3 14B</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="E243" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="F243" t="n">
-        <v>0.052</v>
+        <v>0.24</v>
       </c>
       <c r="G243" t="n">
-        <v>1000000</v>
+        <v>40960</v>
       </c>
       <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>qwen/qwen2.5-vl-72b-instruct</t>
+          <t>qwen/qwen3-235b-a22b-2507</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Qwen: Qwen2.5 VL 72B Instruct</t>
+          <t>Qwen: Qwen3 235B A22B Instruct 2507</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>0.8</v>
+        <v>0.09</v>
       </c>
       <c r="E244" t="n">
-        <v>1</v>
-      </c>
-      <c r="F244" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="G244" t="n">
-        <v>128000</v>
+        <v>262144</v>
       </c>
       <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>qwen/qwen3-14b</t>
+          <t>qwen/qwen3-235b-a22b-thinking-2507</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 14B</t>
+          <t>Qwen: Qwen3 235B A22B Thinking 2507</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>0.12</v>
+        <v>0.45</v>
       </c>
       <c r="E245" t="n">
-        <v>0.24</v>
+        <v>3.5</v>
       </c>
       <c r="G245" t="n">
-        <v>40960</v>
+        <v>128000</v>
       </c>
       <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>qwen/qwen3-235b-a22b-2507</t>
+          <t>qwen/qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 235B A22B Instruct 2507</t>
+          <t>Qwen: Qwen3 30B A3B</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="E246" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="G246" t="n">
-        <v>262144</v>
+        <v>40960</v>
       </c>
       <c r="H246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>qwen/qwen3-235b-a22b-thinking-2507</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 235B A22B Thinking 2507</t>
+          <t>Qwen: Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="E247" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="G247" t="n">
-        <v>128000</v>
+        <v>262144</v>
       </c>
       <c r="H247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b</t>
+          <t>qwen/qwen3-32b</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 30B A3B</t>
+          <t>Qwen: Qwen3 32B</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7703,37 +7703,40 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="E248" t="n">
-        <v>0.5</v>
+        <v>0.28</v>
       </c>
       <c r="G248" t="n">
-        <v>40960</v>
+        <v>131072</v>
       </c>
       <c r="H248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>qwen/qwen3-coder</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 30B A3B Instruct 2507</t>
+          <t>Qwen: Qwen3 Coder 480B A35B</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="D249" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1</v>
+      </c>
+      <c r="F249" t="n">
         <v>0.1</v>
-      </c>
-      <c r="E249" t="n">
-        <v>0.3</v>
       </c>
       <c r="G249" t="n">
         <v>262144</v>
@@ -7743,81 +7746,84 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>qwen/qwen3-32b</t>
+          <t>qwen/qwen3-coder-30b-a3b-instruct</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 32B</t>
+          <t>Qwen: Qwen3 Coder 30B A3B Instruct</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E250" t="n">
         <v>0.28</v>
       </c>
       <c r="G250" t="n">
-        <v>131072</v>
+        <v>262144</v>
       </c>
       <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>qwen/qwen3-coder</t>
+          <t>qwen/qwen3-coder-flash</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 Coder 480B A35B</t>
+          <t>Qwen: Qwen3 Coder Flash</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>0.3</v>
+        <v>0.195</v>
       </c>
       <c r="E251" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
       <c r="F251" t="n">
-        <v>0.1</v>
+        <v>0.039</v>
       </c>
       <c r="G251" t="n">
-        <v>262144</v>
+        <v>1000000</v>
       </c>
       <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>qwen/qwen3-coder-30b-a3b-instruct</t>
+          <t>qwen/qwen3-coder-next</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 Coder 30B A3B Instruct</t>
+          <t>Qwen: Qwen3 Coder Next</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="D252" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F252" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="E252" t="n">
-        <v>0.28</v>
       </c>
       <c r="G252" t="n">
         <v>262144</v>
@@ -7827,57 +7833,51 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>qwen/qwen3-coder-flash</t>
+          <t>qwen/qwen3-next-80b-a3b-instruct</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 Coder Flash</t>
+          <t>Qwen: Qwen3 Next 80B A3B Instruct</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>0.195</v>
+        <v>0.09</v>
       </c>
       <c r="E253" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="F253" t="n">
-        <v>0.039</v>
+        <v>1.1</v>
       </c>
       <c r="G253" t="n">
-        <v>1000000</v>
+        <v>262144</v>
       </c>
       <c r="H253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>qwen/qwen3-coder-next</t>
+          <t>qwen/qwen3-next-80b-a3b-thinking</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 Coder Next</t>
+          <t>Qwen: Qwen3 Next 80B A3B Thinking</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="E254" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F254" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="G254" t="n">
         <v>262144</v>
@@ -7887,24 +7887,27 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>qwen/qwen3-next-80b-a3b-instruct</t>
+          <t>qwen/qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 Next 80B A3B Instruct</t>
+          <t>Qwen: Qwen3 VL 235B A22B Instruct</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="E255" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0.1</v>
       </c>
       <c r="G255" t="n">
         <v>262144</v>
@@ -7914,24 +7917,24 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>qwen/qwen3-next-80b-a3b-thinking</t>
+          <t>qwen/qwen3-vl-30b-a3b-instruct</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 Next 80B A3B Thinking</t>
+          <t>Qwen: Qwen3 VL 30B A3B Instruct</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D256" t="n">
         <v>0.15</v>
       </c>
       <c r="E256" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="G256" t="n">
         <v>262144</v>
@@ -7941,27 +7944,24 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>qwen/qwen3-vl-235b-a22b-instruct</t>
+          <t>qwen/qwen3-vl-30b-a3b-thinking</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 VL 235B A22B Instruct</t>
+          <t>Qwen: Qwen3 VL 30B A3B Thinking</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="E257" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F257" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G257" t="n">
         <v>262144</v>
@@ -7971,24 +7971,27 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>qwen/qwen3-vl-30b-a3b-instruct</t>
+          <t>qwen/qwen3-vl-8b-instruct</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 VL 30B A3B Instruct</t>
+          <t>Qwen: Qwen3 VL 8B Instruct</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="E258" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0.12</v>
       </c>
       <c r="G258" t="n">
         <v>262144</v>
@@ -7998,24 +8001,24 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>qwen/qwen3-vl-30b-a3b-thinking</t>
+          <t>qwen/qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 VL 30B A3B Thinking</t>
+          <t>Qwen: Qwen3.5-122B-A10B</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="E259" t="n">
-        <v>1</v>
+        <v>2.08</v>
       </c>
       <c r="G259" t="n">
         <v>262144</v>
@@ -8025,27 +8028,24 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>qwen/qwen3-vl-8b-instruct</t>
+          <t>qwen/qwen3.5-27b</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3 VL 8B Instruct</t>
+          <t>Qwen: Qwen3.5-27B</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="E260" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F260" t="n">
-        <v>0.12</v>
+        <v>2.6</v>
       </c>
       <c r="G260" t="n">
         <v>262144</v>
@@ -8055,12 +8055,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-122b-a10b</t>
+          <t>qwen/qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.5-122B-A10B</t>
+          <t>Qwen: Qwen3.5-35B-A3B</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8069,10 +8069,13 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="E261" t="n">
-        <v>2.08</v>
+        <v>1</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0.05</v>
       </c>
       <c r="G261" t="n">
         <v>262144</v>
@@ -8082,24 +8085,27 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-27b</t>
+          <t>qwen/qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.5-27B</t>
+          <t>Qwen: Qwen3.5 397B A17B</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="E262" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0.3</v>
       </c>
       <c r="G262" t="n">
         <v>262144</v>
@@ -8109,27 +8115,24 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-35b-a3b</t>
+          <t>qwen/qwen3.5-9b</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.5-35B-A3B</t>
+          <t>Qwen: Qwen3.5-9B</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="E263" t="n">
-        <v>1</v>
-      </c>
-      <c r="F263" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="G263" t="n">
         <v>262144</v>
@@ -8139,81 +8142,78 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-397b-a17b</t>
+          <t>qwen/qwen3.5-flash-02-23</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.5 397B A17B</t>
+          <t>Qwen: Qwen3.5-Flash</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>0.5</v>
+        <v>0.065</v>
       </c>
       <c r="E264" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F264" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="G264" t="n">
-        <v>262144</v>
+        <v>1000000</v>
       </c>
       <c r="H264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-9b</t>
+          <t>qwen/qwen3.5-plus-02-15</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.5-9B</t>
+          <t>Qwen: Qwen3.5 Plus 2026-02-15</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="E265" t="n">
-        <v>0.25</v>
+        <v>1.56</v>
       </c>
       <c r="G265" t="n">
-        <v>262144</v>
+        <v>1000000</v>
       </c>
       <c r="H265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-flash-02-23</t>
+          <t>qwen/qwen3.5-plus-20260420</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.5-Flash</t>
+          <t>Qwen: Qwen3.5 Plus 2026-04-20</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0.065</v>
+        <v>0.3</v>
       </c>
       <c r="E266" t="n">
-        <v>0.26</v>
+        <v>1.8</v>
       </c>
       <c r="G266" t="n">
         <v>1000000</v>
@@ -8223,39 +8223,39 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-plus-02-15</t>
+          <t>qwen/qwen3.6-27b</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.5 Plus 2026-02-15</t>
+          <t>Qwen: Qwen3.6 27B</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="E267" t="n">
-        <v>1.56</v>
+        <v>3.2</v>
       </c>
       <c r="G267" t="n">
-        <v>1000000</v>
+        <v>262144</v>
       </c>
       <c r="H267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-plus-20260420</t>
+          <t>qwen/qwen3.6-35b-a3b</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.5 Plus 2026-04-20</t>
+          <t>Qwen: Qwen3.6 35B A3B</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8264,25 +8264,28 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E268" t="n">
-        <v>1.8</v>
+        <v>0.95</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0.05</v>
       </c>
       <c r="G268" t="n">
-        <v>1000000</v>
+        <v>262144</v>
       </c>
       <c r="H268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>qwen/qwen3.6-27b</t>
+          <t>qwen/qwen3.6-flash</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.6 27B</t>
+          <t>Qwen: Qwen3.6 Flash</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8291,67 +8294,67 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>0.32</v>
+        <v>0.1875</v>
       </c>
       <c r="E269" t="n">
-        <v>3.2</v>
+        <v>1.125</v>
       </c>
       <c r="G269" t="n">
-        <v>262144</v>
+        <v>1000000</v>
       </c>
       <c r="H269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>qwen/qwen3.6-35b-a3b</t>
+          <t>qwen/qwen3.6-plus</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.6 35B A3B</t>
+          <t>Qwen: Qwen3.6 Plus</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>0.1</v>
+        <v>0.325</v>
       </c>
       <c r="E270" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F270" t="n">
-        <v>0.05</v>
+        <v>1.95</v>
       </c>
       <c r="G270" t="n">
-        <v>262144</v>
+        <v>1000000</v>
       </c>
       <c r="H270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>qwen/qwen3.6-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.6 Flash</t>
+          <t>Qwen: Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>0.1875</v>
+        <v>0.03</v>
       </c>
       <c r="E271" t="n">
-        <v>1.125</v>
+        <v>0.13</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0.006</v>
       </c>
       <c r="G271" t="n">
         <v>1000000</v>
@@ -8361,24 +8364,27 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>qwen/qwen3.6-plus</t>
+          <t>qwen/qwen3.7-max</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.6 Plus</t>
+          <t>Qwen: Qwen3.7 Max</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>0.325</v>
+        <v>1.475</v>
       </c>
       <c r="E272" t="n">
-        <v>1.95</v>
+        <v>4.425</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0.295</v>
       </c>
       <c r="G272" t="n">
         <v>1000000</v>
@@ -8388,27 +8394,27 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3.7-plus</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.7 Flash</t>
+          <t>Qwen: Qwen3.7 Plus</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0.03</v>
+        <v>0.32</v>
       </c>
       <c r="E273" t="n">
-        <v>0.13</v>
+        <v>1.28</v>
       </c>
       <c r="F273" t="n">
-        <v>0.006</v>
+        <v>0.064</v>
       </c>
       <c r="G273" t="n">
         <v>1000000</v>
@@ -8418,144 +8424,144 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-max</t>
+          <t>qwen/qwen3.7-plus:batch</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.7 Max</t>
+          <t>Qwen: Qwen3.7 Plus (batch)</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1.475</v>
+        <v>0.23</v>
       </c>
       <c r="E274" t="n">
-        <v>4.425</v>
-      </c>
-      <c r="F274" t="n">
-        <v>0.295</v>
+        <v>0.92</v>
       </c>
       <c r="G274" t="n">
-        <v>1000000</v>
+        <v>262144</v>
       </c>
       <c r="H274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-plus</t>
+          <t>qwen/qwen3.8-2.4t-a95b</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.7 Plus</t>
+          <t>Qwen: Qwen3.8 2.4T A95B</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>0.32</v>
+        <v>2</v>
       </c>
       <c r="E275" t="n">
-        <v>1.28</v>
+        <v>6</v>
       </c>
       <c r="F275" t="n">
-        <v>0.064</v>
+        <v>0.25</v>
       </c>
       <c r="G275" t="n">
-        <v>1000000</v>
+        <v>1048576</v>
       </c>
       <c r="H275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-plus:batch</t>
+          <t>qwen/qwen3.8-27b</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.7 Plus (batch)</t>
+          <t>Qwen: Qwen3.8 27B</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="E276" t="n">
-        <v>0.92</v>
+        <v>2.5</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0.09</v>
       </c>
       <c r="G276" t="n">
-        <v>262144</v>
+        <v>1000000</v>
       </c>
       <c r="H276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-2.4t-a95b</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.8 2.4T A95B</t>
+          <t>Qwen: Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>2</v>
+        <v>0.15</v>
       </c>
       <c r="E277" t="n">
-        <v>6</v>
+        <v>0.47</v>
       </c>
       <c r="F277" t="n">
-        <v>0.25</v>
+        <v>0.016</v>
       </c>
       <c r="G277" t="n">
-        <v>1048576</v>
+        <v>1000000</v>
       </c>
       <c r="H277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-27b</t>
+          <t>qwen/qwen3.8-max-0902</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.8 27B</t>
+          <t>Qwen: Qwen3.8 Max (0902)</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="E278" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="F278" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="G278" t="n">
         <v>1000000</v>
@@ -8565,27 +8571,27 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.8-max-prime</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.8 Flash</t>
+          <t>Qwen: Qwen3.8 Max Prime</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>0.15</v>
+        <v>4</v>
       </c>
       <c r="E279" t="n">
-        <v>0.47</v>
+        <v>12</v>
       </c>
       <c r="F279" t="n">
-        <v>0.016</v>
+        <v>0.5</v>
       </c>
       <c r="G279" t="n">
         <v>1000000</v>
@@ -8595,27 +8601,27 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-max-0902</t>
+          <t>qwen/qwen3.8-omni-flash</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.8 Max (0902)</t>
+          <t>Qwen: Qwen3.8 Omni Flash</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>2</v>
+        <v>0.15</v>
       </c>
       <c r="E280" t="n">
-        <v>6</v>
+        <v>0.47</v>
       </c>
       <c r="F280" t="n">
-        <v>0.25</v>
+        <v>0.016</v>
       </c>
       <c r="G280" t="n">
         <v>1000000</v>
@@ -8625,77 +8631,77 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-max-prime</t>
+          <t>x-ai/grok-4.20</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.8 Max Prime</t>
+          <t>SpaceXAI: Grok 4.20</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="E281" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="F281" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G281" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="H281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-omni-flash</t>
+          <t>x-ai/grok-4.20-multi-agent</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Qwen: Qwen3.8 Omni Flash</t>
+          <t>SpaceXAI: Grok 4.20 Multi-Agent</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>0.15</v>
+        <v>1.25</v>
       </c>
       <c r="E282" t="n">
-        <v>0.47</v>
+        <v>2.5</v>
       </c>
       <c r="F282" t="n">
-        <v>0.016</v>
+        <v>0.2</v>
       </c>
       <c r="G282" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="H282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.20</t>
+          <t>x-ai/grok-4.3</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SpaceXAI: Grok 4.20</t>
+          <t>SpaceXAI: Grok 4.3</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -8708,114 +8714,114 @@
         <v>0.2</v>
       </c>
       <c r="G283" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="H283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.20-multi-agent</t>
+          <t>x-ai/grok-4.3:batch</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SpaceXAI: Grok 4.20 Multi-Agent</t>
+          <t>SpaceXAI: Grok 4.3 (batch)</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E284" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F284" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="G284" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="H284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.3</t>
+          <t>x-ai/grok-4.5</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>SpaceXAI: Grok 4.3</t>
+          <t>SpaceXAI: Grok 4.5</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="E285" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="F285" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G285" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="H285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.3:batch</t>
+          <t>x-ai/grok-4.6</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>SpaceXAI: Grok 4.3 (batch)</t>
+          <t>SpaceXAI: Grok 4.6</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E286" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F286" t="n">
-        <v>0.16</v>
+        <v>0.5</v>
       </c>
       <c r="G286" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="H286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.5</t>
+          <t>x-ai/grok-4.7</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>SpaceXAI: Grok 4.5</t>
+          <t>SpaceXAI: Grok 4.7</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -8825,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="F287" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G287" t="n">
         <v>500000</v>
@@ -8835,207 +8841,207 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.6</t>
+          <t>x-ai/grok-build-0.1</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>SpaceXAI: Grok 4.6</t>
+          <t>SpaceXAI: Grok Build 0.1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="D288" t="n">
+        <v>1</v>
+      </c>
+      <c r="E288" t="n">
         <v>2</v>
       </c>
-      <c r="E288" t="n">
-        <v>6</v>
-      </c>
       <c r="F288" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G288" t="n">
-        <v>500000</v>
+        <v>256000</v>
       </c>
       <c r="H288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.7</t>
+          <t>z-ai/glm-4.5</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>SpaceXAI: Grok 4.7</t>
+          <t>Z.ai: GLM 4.5</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="E289" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="F289" t="n">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
       <c r="G289" t="n">
-        <v>500000</v>
+        <v>131072</v>
       </c>
       <c r="H289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>x-ai/grok-build-0.1</t>
+          <t>z-ai/glm-4.5-air</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>SpaceXAI: Grok Build 0.1</t>
+          <t>Z.ai: GLM 4.5 Air</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>0.13</v>
       </c>
       <c r="E290" t="n">
-        <v>2</v>
+        <v>0.85</v>
       </c>
       <c r="F290" t="n">
-        <v>0.2</v>
+        <v>0.025</v>
       </c>
       <c r="G290" t="n">
-        <v>256000</v>
+        <v>131072</v>
       </c>
       <c r="H290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>z-ai/glm-4.5</t>
+          <t>z-ai/glm-4.5v</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 4.5</t>
+          <t>Z.ai: GLM 4.5V</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="D291" t="n">
         <v>0.6</v>
       </c>
       <c r="E291" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="F291" t="n">
         <v>0.11</v>
       </c>
       <c r="G291" t="n">
-        <v>131072</v>
+        <v>65536</v>
       </c>
       <c r="H291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>z-ai/glm-4.5-air</t>
+          <t>z-ai/glm-4.6</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 4.5 Air</t>
+          <t>Z.ai: GLM 4.6</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0.13</v>
+        <v>0.55</v>
       </c>
       <c r="E292" t="n">
-        <v>0.85</v>
+        <v>2.2</v>
       </c>
       <c r="F292" t="n">
-        <v>0.025</v>
+        <v>0.11</v>
       </c>
       <c r="G292" t="n">
-        <v>131072</v>
+        <v>204800</v>
       </c>
       <c r="H292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>z-ai/glm-4.5v</t>
+          <t>z-ai/glm-4.6v</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 4.5V</t>
+          <t>Z.ai: GLM 4.6V</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E293" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="F293" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="G293" t="n">
-        <v>65536</v>
+        <v>131072</v>
       </c>
       <c r="H293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>z-ai/glm-4.6</t>
+          <t>z-ai/glm-4.7</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 4.6</t>
+          <t>Z.ai: GLM 4.7</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="E294" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="F294" t="n">
-        <v>0.11</v>
+        <v>0.099</v>
       </c>
       <c r="G294" t="n">
         <v>204800</v>
@@ -9045,57 +9051,54 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>z-ai/glm-4.6v</t>
+          <t>z-ai/glm-4.7-flash</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 4.6V</t>
+          <t>Z.ai: GLM 4.7 Flash</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0.3</v>
+        <v>0.0605</v>
       </c>
       <c r="E295" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F295" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G295" t="n">
-        <v>131072</v>
+        <v>200000</v>
       </c>
       <c r="H295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>z-ai/glm-4.7</t>
+          <t>z-ai/glm-5</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 4.7</t>
+          <t>Z.ai: GLM 5</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="E296" t="n">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="F296" t="n">
-        <v>0.099</v>
+        <v>0.2</v>
       </c>
       <c r="G296" t="n">
         <v>204800</v>
@@ -9105,54 +9108,57 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>z-ai/glm-4.7-flash</t>
+          <t>z-ai/glm-5-turbo</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 4.7 Flash</t>
+          <t>Z.ai: GLM 5 Turbo</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0.0605</v>
+        <v>1.2</v>
       </c>
       <c r="E297" t="n">
-        <v>0.4</v>
+        <v>4</v>
+      </c>
+      <c r="F297" t="n">
+        <v>0.24</v>
       </c>
       <c r="G297" t="n">
-        <v>200000</v>
+        <v>202752</v>
       </c>
       <c r="H297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>z-ai/glm-5</t>
+          <t>z-ai/glm-5.1</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 5</t>
+          <t>Z.ai: GLM 5.1</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1</v>
+        <v>0.966</v>
       </c>
       <c r="E298" t="n">
-        <v>3.2</v>
+        <v>3.036</v>
       </c>
       <c r="F298" t="n">
-        <v>0.2</v>
+        <v>0.1794</v>
       </c>
       <c r="G298" t="n">
         <v>204800</v>
@@ -9162,87 +9168,87 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>z-ai/glm-5-turbo</t>
+          <t>z-ai/glm-5.2</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 5 Turbo</t>
+          <t>Z.ai: GLM 5.2</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1.2</v>
+        <v>0.0341</v>
       </c>
       <c r="E299" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F299" t="n">
-        <v>0.24</v>
+        <v>0.033</v>
       </c>
       <c r="G299" t="n">
-        <v>202752</v>
+        <v>1048576</v>
       </c>
       <c r="H299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.1</t>
+          <t>z-ai/glm-5.3</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 5.1</t>
+          <t>Z.ai: GLM 5.3</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0.966</v>
+        <v>0.0699</v>
       </c>
       <c r="E300" t="n">
-        <v>3.036</v>
+        <v>1.4</v>
       </c>
       <c r="F300" t="n">
-        <v>0.1794</v>
+        <v>0.0689</v>
       </c>
       <c r="G300" t="n">
-        <v>204800</v>
+        <v>1048576</v>
       </c>
       <c r="H300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.2</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 5.2</t>
+          <t>Z.ai: GLM 5.3 Flash</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0.0341</v>
+        <v>0.15</v>
       </c>
       <c r="E301" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="F301" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="G301" t="n">
         <v>1048576</v>
@@ -9252,27 +9258,27 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3</t>
+          <t>z-ai/glm-5.3-flash:batch</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 5.3</t>
+          <t>Z.ai: GLM 5.3 Flash (batch)</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0.0699</v>
+        <v>0.05</v>
       </c>
       <c r="E302" t="n">
-        <v>1.4</v>
+        <v>0.18</v>
       </c>
       <c r="F302" t="n">
-        <v>0.0689</v>
+        <v>0.01</v>
       </c>
       <c r="G302" t="n">
         <v>1048576</v>
@@ -9282,27 +9288,27 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>z-ai/glm-5.3-flashx</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 5.3 Flash</t>
+          <t>Z.ai: GLM 5.3 FlashX</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>0.15</v>
+        <v>0.37</v>
       </c>
       <c r="E303" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="F303" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="G303" t="n">
         <v>1048576</v>
@@ -9312,57 +9318,57 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash:batch</t>
+          <t>z-ai/glm-5.3-prime</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 5.3 Flash (batch)</t>
+          <t>Z.ai: GLM 5.3 Prime</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>0.05</v>
+        <v>2.8</v>
       </c>
       <c r="E304" t="n">
-        <v>0.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F304" t="n">
-        <v>0.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G304" t="n">
-        <v>1048576</v>
+        <v>1000000</v>
       </c>
       <c r="H304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flashx</t>
+          <t>z-ai/glm-5.3:batch</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 5.3 FlashX</t>
+          <t>Z.ai: GLM 5.3 (batch)</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="E305" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="F305" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G305" t="n">
         <v>1048576</v>
@@ -9372,92 +9378,32 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-prime</t>
+          <t>z-ai/glm-5v-turbo</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Z.ai: GLM 5.3 Prime</t>
+          <t>Z.ai: GLM 5V Turbo</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="E306" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="F306" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="G306" t="n">
-        <v>1000000</v>
+        <v>202752</v>
       </c>
       <c r="H306" t="inlineStr"/>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>z-ai/glm-5.3:batch</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Z.ai: GLM 5.3 (batch)</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="D307" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E307" t="n">
-        <v>2</v>
-      </c>
-      <c r="F307" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G307" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="H307" t="inlineStr"/>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>z-ai/glm-5v-turbo</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Z.ai: GLM 5V Turbo</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="D308" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E308" t="n">
-        <v>4</v>
-      </c>
-      <c r="F308" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G308" t="n">
-        <v>202752</v>
-      </c>
-      <c r="H308" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
